--- a/artfynd/A 22053-2021 artfynd.xlsx
+++ b/artfynd/A 22053-2021 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>124894896</v>
+        <v>124894199</v>
       </c>
       <c r="B2" t="n">
-        <v>79920</v>
+        <v>79891</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,25 +687,25 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6462</v>
+        <v>6458</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>477763</v>
+        <v>477872</v>
       </c>
       <c r="R2" t="n">
-        <v>6600590</v>
+        <v>6600787</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -750,7 +750,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>13:51</t>
+          <t>13:27</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -760,12 +760,12 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>13:51</t>
+          <t>13:27</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>På gammal rönn.</t>
+          <t>På senvuxen asp.</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -792,10 +792,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>124891426</v>
+        <v>124894766</v>
       </c>
       <c r="B3" t="n">
-        <v>56722</v>
+        <v>79920</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -808,53 +808,34 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100138</v>
+        <v>6462</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L3" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>äldre spillning</t>
-        </is>
-      </c>
+          <t>(Spreng.) Tuck.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
           <t>Krontorp, Krontorp, Vstm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>477819</v>
+        <v>477763</v>
       </c>
       <c r="R3" t="n">
-        <v>6600933</v>
+        <v>6600615</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -886,7 +867,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>11:51</t>
+          <t>13:47</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -896,7 +877,12 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>11:51</t>
+          <t>13:47</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>På senvuxen skogslönn.</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -923,10 +909,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>124891456</v>
+        <v>124895297</v>
       </c>
       <c r="B4" t="n">
-        <v>56722</v>
+        <v>79891</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -935,57 +921,41 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100138</v>
+        <v>6458</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K4" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L4" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr"/>
+      <c r="K4" t="inlineStr"/>
+      <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
           <t>Krontorp, Krontorp, Vstm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>477820</v>
+        <v>477767</v>
       </c>
       <c r="R4" t="n">
-        <v>6600930</v>
+        <v>6600581</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1017,7 +987,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>11:51</t>
+          <t>14:02</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1027,7 +997,12 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>11:51</t>
+          <t>14:02</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>På lönnlåga.</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1036,6 +1011,7 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
+      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
@@ -1054,10 +1030,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>124894766</v>
+        <v>124895742</v>
       </c>
       <c r="B5" t="n">
-        <v>79920</v>
+        <v>57529</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1066,38 +1042,52 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6462</v>
+        <v>100049</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Krontorp, Krontorp, Vstm</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>477763</v>
+        <v>477824</v>
       </c>
       <c r="R5" t="n">
-        <v>6600615</v>
+        <v>6600570</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1129,7 +1119,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>13:47</t>
+          <t>14:17</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1139,12 +1129,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>13:47</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>På senvuxen skogslönn.</t>
+          <t>14:17</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1171,10 +1156,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>124896501</v>
+        <v>124895691</v>
       </c>
       <c r="B6" t="n">
-        <v>79891</v>
+        <v>79920</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1183,25 +1168,25 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6458</v>
+        <v>6462</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1211,10 +1196,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>477773</v>
+        <v>477824</v>
       </c>
       <c r="R6" t="n">
-        <v>6600569</v>
+        <v>6600570</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1246,7 +1231,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>14:42</t>
+          <t>14:14</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1256,12 +1241,12 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>14:42</t>
+          <t>14:14</t>
         </is>
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>På lönnlåga.</t>
+          <t>På senvuxen rönn.</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1288,7 +1273,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>124894199</v>
+        <v>124896501</v>
       </c>
       <c r="B7" t="n">
         <v>79891</v>
@@ -1328,10 +1313,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>477872</v>
+        <v>477773</v>
       </c>
       <c r="R7" t="n">
-        <v>6600787</v>
+        <v>6600569</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1363,7 +1348,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>13:27</t>
+          <t>14:42</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1373,12 +1358,12 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>13:27</t>
+          <t>14:42</t>
         </is>
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>På senvuxen asp.</t>
+          <t>På lönnlåga.</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1405,7 +1390,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>124891544</v>
+        <v>124891456</v>
       </c>
       <c r="B8" t="n">
         <v>56722</v>
@@ -1455,7 +1440,7 @@
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>äldre spillning</t>
+          <t>färsk spillning</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
@@ -1464,10 +1449,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>477831</v>
+        <v>477820</v>
       </c>
       <c r="R8" t="n">
-        <v>6600928</v>
+        <v>6600930</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1499,7 +1484,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>11:53</t>
+          <t>11:51</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1509,7 +1494,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>11:53</t>
+          <t>11:51</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1536,10 +1521,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>124895150</v>
+        <v>124895183</v>
       </c>
       <c r="B9" t="n">
-        <v>79891</v>
+        <v>79851</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1548,38 +1533,41 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6458</v>
+        <v>229497</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
+      <c r="J9" t="inlineStr"/>
+      <c r="K9" t="inlineStr"/>
+      <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Krontorp, Krontorp, Vstm</t>
+          <t>Krontorp, Vstm</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>477767</v>
+        <v>477758</v>
       </c>
       <c r="R9" t="n">
-        <v>6600581</v>
+        <v>6600583</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1611,7 +1599,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>13:59</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1621,7 +1609,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>13:59</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="AC9" t="inlineStr">
@@ -1635,6 +1623,7 @@
       <c r="AE9" t="b">
         <v>0</v>
       </c>
+      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
       </c>
@@ -1653,10 +1642,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>124895691</v>
+        <v>124891544</v>
       </c>
       <c r="B10" t="n">
-        <v>79920</v>
+        <v>56722</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1669,34 +1658,53 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6462</v>
+        <v>100138</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr"/>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>äldre spillning</t>
+        </is>
+      </c>
       <c r="P10" t="inlineStr">
         <is>
           <t>Krontorp, Krontorp, Vstm</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>477824</v>
+        <v>477831</v>
       </c>
       <c r="R10" t="n">
-        <v>6600570</v>
+        <v>6600928</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1728,7 +1736,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>14:14</t>
+          <t>11:53</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1738,12 +1746,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>14:14</t>
-        </is>
-      </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>På senvuxen rönn.</t>
+          <t>11:53</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1770,10 +1773,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>124895742</v>
+        <v>124891426</v>
       </c>
       <c r="B11" t="n">
-        <v>57529</v>
+        <v>56722</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1782,25 +1785,25 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100049</v>
+        <v>100138</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -1813,9 +1816,14 @@
           <t>adult</t>
         </is>
       </c>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>äldre spillning</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
@@ -1824,10 +1832,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>477824</v>
+        <v>477819</v>
       </c>
       <c r="R11" t="n">
-        <v>6600570</v>
+        <v>6600933</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1859,7 +1867,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>14:17</t>
+          <t>11:51</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1869,7 +1877,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>14:17</t>
+          <t>11:51</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1896,10 +1904,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>124895183</v>
+        <v>124894896</v>
       </c>
       <c r="B12" t="n">
-        <v>79851</v>
+        <v>79920</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1912,37 +1920,34 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>229497</v>
+        <v>6462</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
-      <c r="J12" t="inlineStr"/>
-      <c r="K12" t="inlineStr"/>
-      <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Krontorp, Vstm</t>
+          <t>Krontorp, Krontorp, Vstm</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>477758</v>
+        <v>477763</v>
       </c>
       <c r="R12" t="n">
-        <v>6600583</v>
+        <v>6600590</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1974,7 +1979,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>13:51</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1984,12 +1989,12 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>13:51</t>
         </is>
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>På senvuxen skogslönn.</t>
+          <t>På gammal rönn.</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1998,7 +2003,6 @@
       <c r="AE12" t="b">
         <v>0</v>
       </c>
-      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 22053-2021 artfynd.xlsx
+++ b/artfynd/A 22053-2021 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>124894199</v>
+        <v>124896501</v>
       </c>
       <c r="B2" t="n">
         <v>79891</v>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>477872</v>
+        <v>477773</v>
       </c>
       <c r="R2" t="n">
-        <v>6600787</v>
+        <v>6600569</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -750,7 +750,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>13:27</t>
+          <t>14:42</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -760,12 +760,12 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>13:27</t>
+          <t>14:42</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>På senvuxen asp.</t>
+          <t>På lönnlåga.</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -792,10 +792,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>124894766</v>
+        <v>124891544</v>
       </c>
       <c r="B3" t="n">
-        <v>79920</v>
+        <v>56722</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -808,34 +808,53 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6462</v>
+        <v>100138</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>äldre spillning</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Krontorp, Krontorp, Vstm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>477763</v>
+        <v>477831</v>
       </c>
       <c r="R3" t="n">
-        <v>6600615</v>
+        <v>6600928</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -867,7 +886,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>13:47</t>
+          <t>11:53</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -877,12 +896,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>13:47</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>På senvuxen skogslönn.</t>
+          <t>11:53</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -909,7 +923,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>124895297</v>
+        <v>124894199</v>
       </c>
       <c r="B4" t="n">
         <v>79891</v>
@@ -943,19 +957,16 @@
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="J4" t="inlineStr"/>
-      <c r="K4" t="inlineStr"/>
-      <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
           <t>Krontorp, Krontorp, Vstm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>477767</v>
+        <v>477872</v>
       </c>
       <c r="R4" t="n">
-        <v>6600581</v>
+        <v>6600787</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -987,7 +998,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>14:02</t>
+          <t>13:27</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -997,12 +1008,12 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>14:02</t>
+          <t>13:27</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>På lönnlåga.</t>
+          <t>På senvuxen asp.</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1011,7 +1022,6 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
-      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
@@ -1156,10 +1166,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>124895691</v>
+        <v>124895297</v>
       </c>
       <c r="B6" t="n">
-        <v>79920</v>
+        <v>79891</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1168,38 +1178,41 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6462</v>
+        <v>6458</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr"/>
+      <c r="K6" t="inlineStr"/>
+      <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
           <t>Krontorp, Krontorp, Vstm</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>477824</v>
+        <v>477767</v>
       </c>
       <c r="R6" t="n">
-        <v>6600570</v>
+        <v>6600581</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1231,7 +1244,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>14:14</t>
+          <t>14:02</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1241,12 +1254,12 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>14:14</t>
+          <t>14:02</t>
         </is>
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>På senvuxen rönn.</t>
+          <t>På lönnlåga.</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1255,6 +1268,7 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
+      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
@@ -1273,10 +1287,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>124896501</v>
+        <v>124894766</v>
       </c>
       <c r="B7" t="n">
-        <v>79891</v>
+        <v>79920</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1285,25 +1299,25 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6458</v>
+        <v>6462</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1313,10 +1327,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>477773</v>
+        <v>477763</v>
       </c>
       <c r="R7" t="n">
-        <v>6600569</v>
+        <v>6600615</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1348,7 +1362,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>14:42</t>
+          <t>13:47</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1358,12 +1372,12 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>14:42</t>
+          <t>13:47</t>
         </is>
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>På lönnlåga.</t>
+          <t>På senvuxen skogslönn.</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1390,10 +1404,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>124891456</v>
+        <v>124895183</v>
       </c>
       <c r="B8" t="n">
-        <v>56722</v>
+        <v>79851</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1406,53 +1420,37 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100138</v>
+        <v>229497</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K8" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L8" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
+          <t>(Ach.) Müll.Arg.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="J8" t="inlineStr"/>
+      <c r="K8" t="inlineStr"/>
+      <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Krontorp, Krontorp, Vstm</t>
+          <t>Krontorp, Vstm</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>477820</v>
+        <v>477758</v>
       </c>
       <c r="R8" t="n">
-        <v>6600930</v>
+        <v>6600583</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1484,7 +1482,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>11:51</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1494,7 +1492,12 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>11:51</t>
+          <t>14:00</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>På senvuxen skogslönn.</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1503,6 +1506,7 @@
       <c r="AE8" t="b">
         <v>0</v>
       </c>
+      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>
@@ -1521,10 +1525,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>124895183</v>
+        <v>124895691</v>
       </c>
       <c r="B9" t="n">
-        <v>79851</v>
+        <v>79920</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1537,37 +1541,34 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>229497</v>
+        <v>6462</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
-      <c r="J9" t="inlineStr"/>
-      <c r="K9" t="inlineStr"/>
-      <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Krontorp, Vstm</t>
+          <t>Krontorp, Krontorp, Vstm</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>477758</v>
+        <v>477824</v>
       </c>
       <c r="R9" t="n">
-        <v>6600583</v>
+        <v>6600570</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1599,7 +1600,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>14:14</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1609,12 +1610,12 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>14:14</t>
         </is>
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>På senvuxen skogslönn.</t>
+          <t>På senvuxen rönn.</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1623,7 +1624,6 @@
       <c r="AE9" t="b">
         <v>0</v>
       </c>
-      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
       </c>
@@ -1642,7 +1642,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>124891544</v>
+        <v>124891426</v>
       </c>
       <c r="B10" t="n">
         <v>56722</v>
@@ -1701,10 +1701,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>477831</v>
+        <v>477819</v>
       </c>
       <c r="R10" t="n">
-        <v>6600928</v>
+        <v>6600933</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1736,7 +1736,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>11:53</t>
+          <t>11:51</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1746,7 +1746,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>11:53</t>
+          <t>11:51</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1773,10 +1773,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>124891426</v>
+        <v>124894896</v>
       </c>
       <c r="B11" t="n">
-        <v>56722</v>
+        <v>79920</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1789,53 +1789,34 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100138</v>
+        <v>6462</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K11" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L11" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>äldre spillning</t>
-        </is>
-      </c>
+          <t>(Spreng.) Tuck.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
           <t>Krontorp, Krontorp, Vstm</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>477819</v>
+        <v>477763</v>
       </c>
       <c r="R11" t="n">
-        <v>6600933</v>
+        <v>6600590</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1867,7 +1848,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>11:51</t>
+          <t>13:51</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1877,7 +1858,12 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>11:51</t>
+          <t>13:51</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>På gammal rönn.</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1904,10 +1890,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>124894896</v>
+        <v>124891456</v>
       </c>
       <c r="B12" t="n">
-        <v>79920</v>
+        <v>56722</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1920,34 +1906,53 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6462</v>
+        <v>100138</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr"/>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="P12" t="inlineStr">
         <is>
           <t>Krontorp, Krontorp, Vstm</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>477763</v>
+        <v>477820</v>
       </c>
       <c r="R12" t="n">
-        <v>6600590</v>
+        <v>6600930</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1979,7 +1984,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>13:51</t>
+          <t>11:51</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1989,12 +1994,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>13:51</t>
-        </is>
-      </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>På gammal rönn.</t>
+          <t>11:51</t>
         </is>
       </c>
       <c r="AD12" t="b">

--- a/artfynd/A 22053-2021 artfynd.xlsx
+++ b/artfynd/A 22053-2021 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>124896501</v>
+        <v>124895297</v>
       </c>
       <c r="B2" t="n">
         <v>79891</v>
@@ -709,16 +709,19 @@
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr"/>
+      <c r="K2" t="inlineStr"/>
+      <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
           <t>Krontorp, Krontorp, Vstm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>477773</v>
+        <v>477767</v>
       </c>
       <c r="R2" t="n">
-        <v>6600569</v>
+        <v>6600581</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -750,7 +753,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>14:42</t>
+          <t>14:02</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -760,7 +763,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>14:42</t>
+          <t>14:02</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
@@ -774,6 +777,7 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
+      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
@@ -792,10 +796,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>124891544</v>
+        <v>124895183</v>
       </c>
       <c r="B3" t="n">
-        <v>56722</v>
+        <v>79851</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -808,53 +812,37 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100138</v>
+        <v>229497</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L3" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>äldre spillning</t>
-        </is>
-      </c>
+          <t>(Ach.) Müll.Arg.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr"/>
+      <c r="K3" t="inlineStr"/>
+      <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Krontorp, Krontorp, Vstm</t>
+          <t>Krontorp, Vstm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>477831</v>
+        <v>477758</v>
       </c>
       <c r="R3" t="n">
-        <v>6600928</v>
+        <v>6600583</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -886,7 +874,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>11:53</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -896,7 +884,12 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>11:53</t>
+          <t>14:00</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>På senvuxen skogslönn.</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -905,6 +898,7 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
+      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
@@ -923,10 +917,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>124894199</v>
+        <v>124894896</v>
       </c>
       <c r="B4" t="n">
-        <v>79891</v>
+        <v>79920</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -935,25 +929,25 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6458</v>
+        <v>6462</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -963,10 +957,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>477872</v>
+        <v>477763</v>
       </c>
       <c r="R4" t="n">
-        <v>6600787</v>
+        <v>6600590</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -998,7 +992,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>13:27</t>
+          <t>13:51</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1008,12 +1002,12 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>13:27</t>
+          <t>13:51</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>På senvuxen asp.</t>
+          <t>På gammal rönn.</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1040,10 +1034,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>124895742</v>
+        <v>124896501</v>
       </c>
       <c r="B5" t="n">
-        <v>57529</v>
+        <v>79891</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1056,48 +1050,34 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100049</v>
+        <v>6458</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K5" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
           <t>Krontorp, Krontorp, Vstm</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>477824</v>
+        <v>477773</v>
       </c>
       <c r="R5" t="n">
-        <v>6600570</v>
+        <v>6600569</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1129,7 +1109,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>14:17</t>
+          <t>14:42</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1139,7 +1119,12 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>14:17</t>
+          <t>14:42</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>På lönnlåga.</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1166,10 +1151,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>124895297</v>
+        <v>124891426</v>
       </c>
       <c r="B6" t="n">
-        <v>79891</v>
+        <v>56722</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1178,41 +1163,57 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6458</v>
+        <v>100138</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr"/>
-      <c r="J6" t="inlineStr"/>
-      <c r="K6" t="inlineStr"/>
-      <c r="N6" t="inlineStr"/>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>äldre spillning</t>
+        </is>
+      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>Krontorp, Krontorp, Vstm</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>477767</v>
+        <v>477819</v>
       </c>
       <c r="R6" t="n">
-        <v>6600581</v>
+        <v>6600933</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1244,7 +1245,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>14:02</t>
+          <t>11:51</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1254,12 +1255,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>14:02</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>På lönnlåga.</t>
+          <t>11:51</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1268,7 +1264,6 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
-      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
@@ -1287,10 +1282,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>124894766</v>
+        <v>124894199</v>
       </c>
       <c r="B7" t="n">
-        <v>79920</v>
+        <v>79891</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1299,25 +1294,25 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6462</v>
+        <v>6458</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1327,10 +1322,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>477763</v>
+        <v>477872</v>
       </c>
       <c r="R7" t="n">
-        <v>6600615</v>
+        <v>6600787</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1362,7 +1357,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>13:47</t>
+          <t>13:27</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1372,12 +1367,12 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>13:47</t>
+          <t>13:27</t>
         </is>
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>På senvuxen skogslönn.</t>
+          <t>På senvuxen asp.</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1404,10 +1399,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>124895183</v>
+        <v>124891544</v>
       </c>
       <c r="B8" t="n">
-        <v>79851</v>
+        <v>56722</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1420,37 +1415,53 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>229497</v>
+        <v>100138</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr"/>
-      <c r="J8" t="inlineStr"/>
-      <c r="K8" t="inlineStr"/>
-      <c r="N8" t="inlineStr"/>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>äldre spillning</t>
+        </is>
+      </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Krontorp, Vstm</t>
+          <t>Krontorp, Krontorp, Vstm</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>477758</v>
+        <v>477831</v>
       </c>
       <c r="R8" t="n">
-        <v>6600583</v>
+        <v>6600928</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1482,7 +1493,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>11:53</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1492,12 +1503,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>14:00</t>
-        </is>
-      </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>På senvuxen skogslönn.</t>
+          <t>11:53</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1506,7 +1512,6 @@
       <c r="AE8" t="b">
         <v>0</v>
       </c>
-      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>
@@ -1525,7 +1530,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>124895691</v>
+        <v>124894766</v>
       </c>
       <c r="B9" t="n">
         <v>79920</v>
@@ -1565,10 +1570,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>477824</v>
+        <v>477763</v>
       </c>
       <c r="R9" t="n">
-        <v>6600570</v>
+        <v>6600615</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1600,7 +1605,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>14:14</t>
+          <t>13:47</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1610,12 +1615,12 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>14:14</t>
+          <t>13:47</t>
         </is>
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>På senvuxen rönn.</t>
+          <t>På senvuxen skogslönn.</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1642,10 +1647,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>124891426</v>
+        <v>124895691</v>
       </c>
       <c r="B10" t="n">
-        <v>56722</v>
+        <v>79920</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1658,53 +1663,34 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100138</v>
+        <v>6462</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K10" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L10" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>äldre spillning</t>
-        </is>
-      </c>
+          <t>(Spreng.) Tuck.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
           <t>Krontorp, Krontorp, Vstm</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>477819</v>
+        <v>477824</v>
       </c>
       <c r="R10" t="n">
-        <v>6600933</v>
+        <v>6600570</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1736,7 +1722,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>11:51</t>
+          <t>14:14</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1746,7 +1732,12 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>11:51</t>
+          <t>14:14</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>På senvuxen rönn.</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1773,10 +1764,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>124894896</v>
+        <v>124895742</v>
       </c>
       <c r="B11" t="n">
-        <v>79920</v>
+        <v>57529</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1785,38 +1776,52 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6462</v>
+        <v>100049</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P11" t="inlineStr">
         <is>
           <t>Krontorp, Krontorp, Vstm</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>477763</v>
+        <v>477824</v>
       </c>
       <c r="R11" t="n">
-        <v>6600590</v>
+        <v>6600570</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1848,7 +1853,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>13:51</t>
+          <t>14:17</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1858,12 +1863,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>13:51</t>
-        </is>
-      </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>På gammal rönn.</t>
+          <t>14:17</t>
         </is>
       </c>
       <c r="AD11" t="b">

--- a/artfynd/A 22053-2021 artfynd.xlsx
+++ b/artfynd/A 22053-2021 artfynd.xlsx
@@ -1151,10 +1151,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>124891426</v>
+        <v>124894199</v>
       </c>
       <c r="B6" t="n">
-        <v>56722</v>
+        <v>79891</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1163,57 +1163,38 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100138</v>
+        <v>6458</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K6" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L6" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>äldre spillning</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
           <t>Krontorp, Krontorp, Vstm</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>477819</v>
+        <v>477872</v>
       </c>
       <c r="R6" t="n">
-        <v>6600933</v>
+        <v>6600787</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1245,7 +1226,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>11:51</t>
+          <t>13:27</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1255,7 +1236,12 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>11:51</t>
+          <t>13:27</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>På senvuxen asp.</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1282,10 +1268,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>124894199</v>
+        <v>124894766</v>
       </c>
       <c r="B7" t="n">
-        <v>79891</v>
+        <v>79920</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1294,25 +1280,25 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6458</v>
+        <v>6462</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1322,10 +1308,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>477872</v>
+        <v>477763</v>
       </c>
       <c r="R7" t="n">
-        <v>6600787</v>
+        <v>6600615</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1357,7 +1343,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>13:27</t>
+          <t>13:47</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1367,12 +1353,12 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>13:27</t>
+          <t>13:47</t>
         </is>
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>På senvuxen asp.</t>
+          <t>På senvuxen skogslönn.</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1399,10 +1385,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>124891544</v>
+        <v>124895691</v>
       </c>
       <c r="B8" t="n">
-        <v>56722</v>
+        <v>79920</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1415,53 +1401,34 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100138</v>
+        <v>6462</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K8" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L8" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>äldre spillning</t>
-        </is>
-      </c>
+          <t>(Spreng.) Tuck.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
           <t>Krontorp, Krontorp, Vstm</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>477831</v>
+        <v>477824</v>
       </c>
       <c r="R8" t="n">
-        <v>6600928</v>
+        <v>6600570</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1493,7 +1460,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>11:53</t>
+          <t>14:14</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1503,7 +1470,12 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>11:53</t>
+          <t>14:14</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>På senvuxen rönn.</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1530,14 +1502,14 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>124894766</v>
+        <v>124891544</v>
       </c>
       <c r="B9" t="n">
-        <v>79920</v>
+        <v>56722</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Ovaliderad</t>
+          <t>Behöver inte valideras</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1546,34 +1518,53 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6462</v>
+        <v>100138</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr"/>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>äldre spillning</t>
+        </is>
+      </c>
       <c r="P9" t="inlineStr">
         <is>
           <t>Krontorp, Krontorp, Vstm</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>477763</v>
+        <v>477831</v>
       </c>
       <c r="R9" t="n">
-        <v>6600615</v>
+        <v>6600928</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1605,7 +1596,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>13:47</t>
+          <t>11:53</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1615,12 +1606,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>13:47</t>
-        </is>
-      </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>På senvuxen skogslönn.</t>
+          <t>11:53</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1647,40 +1633,54 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>124895691</v>
+        <v>124895742</v>
       </c>
       <c r="B10" t="n">
-        <v>79920</v>
+        <v>57529</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Ovaliderad</t>
+          <t>Godkänd baserat på observatörens uppgifter</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6462</v>
+        <v>100049</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P10" t="inlineStr">
         <is>
           <t>Krontorp, Krontorp, Vstm</t>
@@ -1722,7 +1722,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>14:14</t>
+          <t>14:17</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1732,12 +1732,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>14:14</t>
-        </is>
-      </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>På senvuxen rönn.</t>
+          <t>14:17</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1764,37 +1759,37 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>124895742</v>
+        <v>124891426</v>
       </c>
       <c r="B11" t="n">
-        <v>57529</v>
+        <v>56722</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Ovaliderad</t>
+          <t>Behöver inte valideras</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100049</v>
+        <v>100138</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -1807,9 +1802,14 @@
           <t>adult</t>
         </is>
       </c>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>äldre spillning</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
@@ -1818,10 +1818,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>477824</v>
+        <v>477819</v>
       </c>
       <c r="R11" t="n">
-        <v>6600570</v>
+        <v>6600933</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1853,7 +1853,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>14:17</t>
+          <t>11:51</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1863,7 +1863,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>14:17</t>
+          <t>11:51</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1897,7 +1897,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Ovaliderad</t>
+          <t>Godkänd baserat på observatörens uppgifter</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">

--- a/artfynd/A 22053-2021 artfynd.xlsx
+++ b/artfynd/A 22053-2021 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>124895297</v>
+        <v>124895691</v>
       </c>
       <c r="B2" t="n">
-        <v>79891</v>
+        <v>79920</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,41 +687,38 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6458</v>
+        <v>6462</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
-      <c r="J2" t="inlineStr"/>
-      <c r="K2" t="inlineStr"/>
-      <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
           <t>Krontorp, Krontorp, Vstm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>477767</v>
+        <v>477824</v>
       </c>
       <c r="R2" t="n">
-        <v>6600581</v>
+        <v>6600570</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -753,7 +750,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>14:02</t>
+          <t>14:14</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -763,12 +760,12 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>14:02</t>
+          <t>14:14</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>På lönnlåga.</t>
+          <t>På senvuxen rönn.</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -777,7 +774,6 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
-      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
@@ -796,10 +792,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>124895183</v>
+        <v>124894199</v>
       </c>
       <c r="B3" t="n">
-        <v>79851</v>
+        <v>79891</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -808,41 +804,38 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>229497</v>
+        <v>6458</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="J3" t="inlineStr"/>
-      <c r="K3" t="inlineStr"/>
-      <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Krontorp, Vstm</t>
+          <t>Krontorp, Krontorp, Vstm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>477758</v>
+        <v>477872</v>
       </c>
       <c r="R3" t="n">
-        <v>6600583</v>
+        <v>6600787</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -874,7 +867,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>13:27</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -884,12 +877,12 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>13:27</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>På senvuxen skogslönn.</t>
+          <t>På senvuxen asp.</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -898,7 +891,6 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
-      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
@@ -917,10 +909,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>124894896</v>
+        <v>124895183</v>
       </c>
       <c r="B4" t="n">
-        <v>79920</v>
+        <v>79851</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -933,34 +925,37 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6462</v>
+        <v>229497</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr"/>
+      <c r="K4" t="inlineStr"/>
+      <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Krontorp, Krontorp, Vstm</t>
+          <t>Krontorp, Vstm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>477763</v>
+        <v>477758</v>
       </c>
       <c r="R4" t="n">
-        <v>6600590</v>
+        <v>6600583</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -992,7 +987,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>13:51</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1002,12 +997,12 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>13:51</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>På gammal rönn.</t>
+          <t>På senvuxen skogslönn.</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1016,6 +1011,7 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
+      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
@@ -1034,10 +1030,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>124896501</v>
+        <v>124894766</v>
       </c>
       <c r="B5" t="n">
-        <v>79891</v>
+        <v>79920</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1046,25 +1042,25 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6458</v>
+        <v>6462</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1074,10 +1070,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>477773</v>
+        <v>477763</v>
       </c>
       <c r="R5" t="n">
-        <v>6600569</v>
+        <v>6600615</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1109,7 +1105,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>14:42</t>
+          <t>13:47</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1119,12 +1115,12 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>14:42</t>
+          <t>13:47</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>På lönnlåga.</t>
+          <t>På senvuxen skogslönn.</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1151,7 +1147,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>124894199</v>
+        <v>124896501</v>
       </c>
       <c r="B6" t="n">
         <v>79891</v>
@@ -1191,10 +1187,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>477872</v>
+        <v>477773</v>
       </c>
       <c r="R6" t="n">
-        <v>6600787</v>
+        <v>6600569</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1226,7 +1222,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>13:27</t>
+          <t>14:42</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1236,12 +1232,12 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>13:27</t>
+          <t>14:42</t>
         </is>
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>På senvuxen asp.</t>
+          <t>På lönnlåga.</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1268,10 +1264,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>124894766</v>
+        <v>124895297</v>
       </c>
       <c r="B7" t="n">
-        <v>79920</v>
+        <v>79891</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1280,38 +1276,41 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6462</v>
+        <v>6458</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
+      <c r="J7" t="inlineStr"/>
+      <c r="K7" t="inlineStr"/>
+      <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
           <t>Krontorp, Krontorp, Vstm</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>477763</v>
+        <v>477767</v>
       </c>
       <c r="R7" t="n">
-        <v>6600615</v>
+        <v>6600581</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1343,7 +1342,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>13:47</t>
+          <t>14:02</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1353,12 +1352,12 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>13:47</t>
+          <t>14:02</t>
         </is>
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>På senvuxen skogslönn.</t>
+          <t>På lönnlåga.</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1367,6 +1366,7 @@
       <c r="AE7" t="b">
         <v>0</v>
       </c>
+      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
@@ -1385,7 +1385,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>124895691</v>
+        <v>124894896</v>
       </c>
       <c r="B8" t="n">
         <v>79920</v>
@@ -1425,10 +1425,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>477824</v>
+        <v>477763</v>
       </c>
       <c r="R8" t="n">
-        <v>6600570</v>
+        <v>6600590</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1460,7 +1460,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>14:14</t>
+          <t>13:51</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1470,12 +1470,12 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>14:14</t>
+          <t>13:51</t>
         </is>
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>På senvuxen rönn.</t>
+          <t>På gammal rönn.</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1502,14 +1502,14 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>124891544</v>
+        <v>124891456</v>
       </c>
       <c r="B9" t="n">
         <v>56722</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Behöver inte valideras</t>
+          <t>Godkänd baserat på observatörens uppgifter</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1552,7 +1552,7 @@
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>äldre spillning</t>
+          <t>färsk spillning</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
@@ -1561,10 +1561,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>477831</v>
+        <v>477820</v>
       </c>
       <c r="R9" t="n">
-        <v>6600928</v>
+        <v>6600930</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1596,7 +1596,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>11:53</t>
+          <t>11:51</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1606,7 +1606,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>11:53</t>
+          <t>11:51</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1759,7 +1759,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>124891426</v>
+        <v>124891544</v>
       </c>
       <c r="B11" t="n">
         <v>56722</v>
@@ -1818,10 +1818,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>477819</v>
+        <v>477831</v>
       </c>
       <c r="R11" t="n">
-        <v>6600933</v>
+        <v>6600928</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1853,7 +1853,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>11:51</t>
+          <t>11:53</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1863,7 +1863,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>11:51</t>
+          <t>11:53</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1890,14 +1890,14 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>124891456</v>
+        <v>124891426</v>
       </c>
       <c r="B12" t="n">
         <v>56722</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Godkänd baserat på observatörens uppgifter</t>
+          <t>Behöver inte valideras</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1940,7 +1940,7 @@
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>färsk spillning</t>
+          <t>äldre spillning</t>
         </is>
       </c>
       <c r="P12" t="inlineStr">
@@ -1949,10 +1949,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>477820</v>
+        <v>477819</v>
       </c>
       <c r="R12" t="n">
-        <v>6600930</v>
+        <v>6600933</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>

--- a/artfynd/A 22053-2021 artfynd.xlsx
+++ b/artfynd/A 22053-2021 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>124895691</v>
+        <v>124894199</v>
       </c>
       <c r="B2" t="n">
-        <v>79920</v>
+        <v>79891</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,25 +687,25 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6462</v>
+        <v>6458</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>477824</v>
+        <v>477872</v>
       </c>
       <c r="R2" t="n">
-        <v>6600570</v>
+        <v>6600787</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -750,7 +750,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>14:14</t>
+          <t>13:27</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -760,12 +760,12 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>14:14</t>
+          <t>13:27</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>På senvuxen rönn.</t>
+          <t>På senvuxen asp.</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -792,7 +792,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>124894199</v>
+        <v>124895150</v>
       </c>
       <c r="B3" t="n">
         <v>79891</v>
@@ -832,10 +832,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>477872</v>
+        <v>477767</v>
       </c>
       <c r="R3" t="n">
-        <v>6600787</v>
+        <v>6600581</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -867,7 +867,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>13:27</t>
+          <t>13:59</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -877,12 +877,12 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>13:27</t>
+          <t>13:59</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>På senvuxen asp.</t>
+          <t>På senvuxen skogslönn.</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -1030,7 +1030,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>124894766</v>
+        <v>124894896</v>
       </c>
       <c r="B5" t="n">
         <v>79920</v>
@@ -1073,7 +1073,7 @@
         <v>477763</v>
       </c>
       <c r="R5" t="n">
-        <v>6600615</v>
+        <v>6600590</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1105,7 +1105,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>13:47</t>
+          <t>13:51</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1115,12 +1115,12 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>13:47</t>
+          <t>13:51</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>På senvuxen skogslönn.</t>
+          <t>På gammal rönn.</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1264,10 +1264,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>124895297</v>
+        <v>124895691</v>
       </c>
       <c r="B7" t="n">
-        <v>79891</v>
+        <v>79920</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1276,41 +1276,38 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6458</v>
+        <v>6462</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="J7" t="inlineStr"/>
-      <c r="K7" t="inlineStr"/>
-      <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
           <t>Krontorp, Krontorp, Vstm</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>477767</v>
+        <v>477824</v>
       </c>
       <c r="R7" t="n">
-        <v>6600581</v>
+        <v>6600570</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1342,7 +1339,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>14:02</t>
+          <t>14:14</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1352,12 +1349,12 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>14:02</t>
+          <t>14:14</t>
         </is>
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>På lönnlåga.</t>
+          <t>På senvuxen rönn.</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1366,7 +1363,6 @@
       <c r="AE7" t="b">
         <v>0</v>
       </c>
-      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
@@ -1385,7 +1381,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>124894896</v>
+        <v>124894766</v>
       </c>
       <c r="B8" t="n">
         <v>79920</v>
@@ -1428,7 +1424,7 @@
         <v>477763</v>
       </c>
       <c r="R8" t="n">
-        <v>6600590</v>
+        <v>6600615</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1460,7 +1456,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>13:51</t>
+          <t>13:47</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1470,12 +1466,12 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>13:51</t>
+          <t>13:47</t>
         </is>
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>På gammal rönn.</t>
+          <t>På senvuxen skogslönn.</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1502,14 +1498,14 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>124891456</v>
+        <v>124891426</v>
       </c>
       <c r="B9" t="n">
         <v>56722</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Godkänd baserat på observatörens uppgifter</t>
+          <t>Behöver inte valideras</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1552,7 +1548,7 @@
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>färsk spillning</t>
+          <t>äldre spillning</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
@@ -1561,10 +1557,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>477820</v>
+        <v>477819</v>
       </c>
       <c r="R9" t="n">
-        <v>6600930</v>
+        <v>6600933</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1633,10 +1629,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>124895742</v>
+        <v>124891456</v>
       </c>
       <c r="B10" t="n">
-        <v>57529</v>
+        <v>56722</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1645,25 +1641,25 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100049</v>
+        <v>100138</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -1676,9 +1672,14 @@
           <t>adult</t>
         </is>
       </c>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färsk spillning</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
@@ -1687,10 +1688,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>477824</v>
+        <v>477820</v>
       </c>
       <c r="R10" t="n">
-        <v>6600570</v>
+        <v>6600930</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1722,7 +1723,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>14:17</t>
+          <t>11:51</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1732,7 +1733,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>14:17</t>
+          <t>11:51</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1759,37 +1760,37 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>124891544</v>
+        <v>124895742</v>
       </c>
       <c r="B11" t="n">
-        <v>56722</v>
+        <v>57529</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Behöver inte valideras</t>
+          <t>Godkänd baserat på observatörens uppgifter</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100138</v>
+        <v>100049</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -1802,14 +1803,9 @@
           <t>adult</t>
         </is>
       </c>
-      <c r="L11" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>äldre spillning</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
@@ -1818,10 +1814,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>477831</v>
+        <v>477824</v>
       </c>
       <c r="R11" t="n">
-        <v>6600928</v>
+        <v>6600570</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1853,7 +1849,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>11:53</t>
+          <t>14:17</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1863,7 +1859,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>11:53</t>
+          <t>14:17</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1890,7 +1886,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>124891426</v>
+        <v>124891544</v>
       </c>
       <c r="B12" t="n">
         <v>56722</v>
@@ -1949,10 +1945,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>477819</v>
+        <v>477831</v>
       </c>
       <c r="R12" t="n">
-        <v>6600933</v>
+        <v>6600928</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1984,7 +1980,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>11:51</t>
+          <t>11:53</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1994,7 +1990,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>11:51</t>
+          <t>11:53</t>
         </is>
       </c>
       <c r="AD12" t="b">

--- a/artfynd/A 22053-2021 artfynd.xlsx
+++ b/artfynd/A 22053-2021 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY12"/>
+  <dimension ref="A1:AY16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2015,6 +2015,430 @@
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>125221042</v>
+      </c>
+      <c r="B13" t="n">
+        <v>79891</v>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Rockesholm, Vstm</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>477797</v>
+      </c>
+      <c r="R13" t="n">
+        <v>6600851</v>
+      </c>
+      <c r="S13" t="n">
+        <v>5</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Hällefors</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Grythyttan</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>2025-04-01</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>2025-04-01</t>
+        </is>
+      </c>
+      <c r="AD13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>125221041</v>
+      </c>
+      <c r="B14" t="n">
+        <v>79892</v>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>2081</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Skrovellav</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Lobaria scrobiculata</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>(Scop.) DC.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>Rockesholm, Vstm</t>
+        </is>
+      </c>
+      <c r="Q14" t="n">
+        <v>477795</v>
+      </c>
+      <c r="R14" t="n">
+        <v>6600854</v>
+      </c>
+      <c r="S14" t="n">
+        <v>5</v>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>Hällefors</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Grythyttan</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>2025-04-01</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>2025-04-01</t>
+        </is>
+      </c>
+      <c r="AD14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT14" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>125221043</v>
+      </c>
+      <c r="B15" t="n">
+        <v>95345</v>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>2810</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Västlig hakmossa</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Rhytidiadelphus loreus</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>(Hedw.) Warnst.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>Rockesholm, Vstm</t>
+        </is>
+      </c>
+      <c r="Q15" t="n">
+        <v>477772</v>
+      </c>
+      <c r="R15" t="n">
+        <v>6600570</v>
+      </c>
+      <c r="S15" t="n">
+        <v>5</v>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>Hällefors</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Grythyttan</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>2025-04-01</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>2025-04-01</t>
+        </is>
+      </c>
+      <c r="AD15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT15" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AX15" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>125221044</v>
+      </c>
+      <c r="B16" t="n">
+        <v>79891</v>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>Rockesholm, Vstm</t>
+        </is>
+      </c>
+      <c r="Q16" t="n">
+        <v>477770</v>
+      </c>
+      <c r="R16" t="n">
+        <v>6600573</v>
+      </c>
+      <c r="S16" t="n">
+        <v>5</v>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>Hällefors</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Grythyttan</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>2025-04-01</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>2025-04-01</t>
+        </is>
+      </c>
+      <c r="AD16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT16" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AX16" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 22053-2021 artfynd.xlsx
+++ b/artfynd/A 22053-2021 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>124894199</v>
+        <v>124894896</v>
       </c>
       <c r="B2" t="n">
-        <v>79891</v>
+        <v>79920</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,25 +687,25 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6458</v>
+        <v>6462</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>477872</v>
+        <v>477763</v>
       </c>
       <c r="R2" t="n">
-        <v>6600787</v>
+        <v>6600590</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -750,7 +750,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>13:27</t>
+          <t>13:51</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -760,12 +760,12 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>13:27</t>
+          <t>13:51</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>På senvuxen asp.</t>
+          <t>På gammal rönn.</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -792,10 +792,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>124895150</v>
+        <v>124895183</v>
       </c>
       <c r="B3" t="n">
-        <v>79891</v>
+        <v>79851</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -804,38 +804,41 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6458</v>
+        <v>229497</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr"/>
+      <c r="K3" t="inlineStr"/>
+      <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Krontorp, Krontorp, Vstm</t>
+          <t>Krontorp, Vstm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>477767</v>
+        <v>477758</v>
       </c>
       <c r="R3" t="n">
-        <v>6600581</v>
+        <v>6600583</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -867,7 +870,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>13:59</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -877,7 +880,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>13:59</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
@@ -891,6 +894,7 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
+      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
@@ -909,10 +913,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>124895183</v>
+        <v>124895297</v>
       </c>
       <c r="B4" t="n">
-        <v>79851</v>
+        <v>79891</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -921,25 +925,25 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>229497</v>
+        <v>6458</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -948,14 +952,14 @@
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Krontorp, Vstm</t>
+          <t>Krontorp, Krontorp, Vstm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>477758</v>
+        <v>477767</v>
       </c>
       <c r="R4" t="n">
-        <v>6600583</v>
+        <v>6600581</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -987,7 +991,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>14:02</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -997,12 +1001,12 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>14:02</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>På senvuxen skogslönn.</t>
+          <t>På lönnlåga.</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1030,10 +1034,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>124894896</v>
+        <v>124896501</v>
       </c>
       <c r="B5" t="n">
-        <v>79920</v>
+        <v>79891</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1042,25 +1046,25 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6462</v>
+        <v>6458</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1070,10 +1074,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>477763</v>
+        <v>477773</v>
       </c>
       <c r="R5" t="n">
-        <v>6600590</v>
+        <v>6600569</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1105,7 +1109,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>13:51</t>
+          <t>14:42</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1115,12 +1119,12 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>13:51</t>
+          <t>14:42</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>På gammal rönn.</t>
+          <t>På lönnlåga.</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1147,10 +1151,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>124896501</v>
+        <v>124894766</v>
       </c>
       <c r="B6" t="n">
-        <v>79891</v>
+        <v>79920</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1159,25 +1163,25 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6458</v>
+        <v>6462</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1187,10 +1191,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>477773</v>
+        <v>477763</v>
       </c>
       <c r="R6" t="n">
-        <v>6600569</v>
+        <v>6600615</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1222,7 +1226,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>14:42</t>
+          <t>13:47</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1232,12 +1236,12 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>14:42</t>
+          <t>13:47</t>
         </is>
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>På lönnlåga.</t>
+          <t>På senvuxen skogslönn.</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1264,10 +1268,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>124895691</v>
+        <v>124894199</v>
       </c>
       <c r="B7" t="n">
-        <v>79920</v>
+        <v>79891</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1276,25 +1280,25 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6462</v>
+        <v>6458</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1304,10 +1308,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>477824</v>
+        <v>477872</v>
       </c>
       <c r="R7" t="n">
-        <v>6600570</v>
+        <v>6600787</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1339,7 +1343,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>14:14</t>
+          <t>13:27</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1349,12 +1353,12 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>14:14</t>
+          <t>13:27</t>
         </is>
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>På senvuxen rönn.</t>
+          <t>På senvuxen asp.</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1381,7 +1385,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>124894766</v>
+        <v>124895691</v>
       </c>
       <c r="B8" t="n">
         <v>79920</v>
@@ -1421,10 +1425,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>477763</v>
+        <v>477824</v>
       </c>
       <c r="R8" t="n">
-        <v>6600615</v>
+        <v>6600570</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1456,7 +1460,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>13:47</t>
+          <t>14:14</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1466,12 +1470,12 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>13:47</t>
+          <t>14:14</t>
         </is>
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>På senvuxen skogslönn.</t>
+          <t>På senvuxen rönn.</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1498,37 +1502,37 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>124891426</v>
+        <v>124895742</v>
       </c>
       <c r="B9" t="n">
-        <v>56722</v>
+        <v>57529</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Behöver inte valideras</t>
+          <t>Godkänd baserat på observatörens uppgifter</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100138</v>
+        <v>100049</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -1541,14 +1545,9 @@
           <t>adult</t>
         </is>
       </c>
-      <c r="L9" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>äldre spillning</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
@@ -1557,10 +1556,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>477819</v>
+        <v>477824</v>
       </c>
       <c r="R9" t="n">
-        <v>6600933</v>
+        <v>6600570</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1592,7 +1591,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>11:51</t>
+          <t>14:17</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1602,7 +1601,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>11:51</t>
+          <t>14:17</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1760,37 +1759,37 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>124895742</v>
+        <v>124891544</v>
       </c>
       <c r="B11" t="n">
-        <v>57529</v>
+        <v>56722</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Godkänd baserat på observatörens uppgifter</t>
+          <t>Behöver inte valideras</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100049</v>
+        <v>100138</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -1803,9 +1802,14 @@
           <t>adult</t>
         </is>
       </c>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>äldre spillning</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
@@ -1814,10 +1818,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>477824</v>
+        <v>477831</v>
       </c>
       <c r="R11" t="n">
-        <v>6600570</v>
+        <v>6600928</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1849,7 +1853,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>14:17</t>
+          <t>11:53</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1859,7 +1863,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>14:17</t>
+          <t>11:53</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1886,7 +1890,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>124891544</v>
+        <v>124891426</v>
       </c>
       <c r="B12" t="n">
         <v>56722</v>
@@ -1945,10 +1949,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>477831</v>
+        <v>477819</v>
       </c>
       <c r="R12" t="n">
-        <v>6600928</v>
+        <v>6600933</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1980,7 +1984,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>11:53</t>
+          <t>11:51</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1990,7 +1994,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>11:53</t>
+          <t>11:51</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -2017,10 +2021,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>125221042</v>
+        <v>125221043</v>
       </c>
       <c r="B13" t="n">
-        <v>79891</v>
+        <v>95345</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -2029,30 +2033,30 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6458</v>
+        <v>2810</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Västlig hakmossa</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Rhytidiadelphus loreus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Hedw.) Warnst.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>1</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
@@ -2061,10 +2065,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>477797</v>
+        <v>477772</v>
       </c>
       <c r="R13" t="n">
-        <v>6600851</v>
+        <v>6600570</v>
       </c>
       <c r="S13" t="n">
         <v>5</v>
@@ -2123,10 +2127,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>125221041</v>
+        <v>125221042</v>
       </c>
       <c r="B14" t="n">
-        <v>79892</v>
+        <v>79891</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2139,26 +2143,26 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>2081</v>
+        <v>6458</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>5</t>
         </is>
       </c>
       <c r="P14" t="inlineStr">
@@ -2167,10 +2171,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>477795</v>
+        <v>477797</v>
       </c>
       <c r="R14" t="n">
-        <v>6600854</v>
+        <v>6600851</v>
       </c>
       <c r="S14" t="n">
         <v>5</v>
@@ -2229,10 +2233,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>125221043</v>
+        <v>125221044</v>
       </c>
       <c r="B15" t="n">
-        <v>95345</v>
+        <v>79891</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2241,30 +2245,30 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>2810</v>
+        <v>6458</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Västlig hakmossa</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Rhytidiadelphus loreus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Hedw.) Warnst.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>5</t>
         </is>
       </c>
       <c r="P15" t="inlineStr">
@@ -2273,10 +2277,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>477772</v>
+        <v>477770</v>
       </c>
       <c r="R15" t="n">
-        <v>6600570</v>
+        <v>6600573</v>
       </c>
       <c r="S15" t="n">
         <v>5</v>
@@ -2335,10 +2339,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>125221044</v>
+        <v>125221041</v>
       </c>
       <c r="B16" t="n">
-        <v>79891</v>
+        <v>79892</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2351,26 +2355,26 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6458</v>
+        <v>2081</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>1</t>
         </is>
       </c>
       <c r="P16" t="inlineStr">
@@ -2379,10 +2383,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>477770</v>
+        <v>477795</v>
       </c>
       <c r="R16" t="n">
-        <v>6600573</v>
+        <v>6600854</v>
       </c>
       <c r="S16" t="n">
         <v>5</v>

--- a/artfynd/A 22053-2021 artfynd.xlsx
+++ b/artfynd/A 22053-2021 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>124894896</v>
+        <v>124895691</v>
       </c>
       <c r="B2" t="n">
         <v>79920</v>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>477763</v>
+        <v>477824</v>
       </c>
       <c r="R2" t="n">
-        <v>6600590</v>
+        <v>6600570</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -750,7 +750,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>13:51</t>
+          <t>14:14</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -760,12 +760,12 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>13:51</t>
+          <t>14:14</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>På gammal rönn.</t>
+          <t>På senvuxen rönn.</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -1034,7 +1034,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>124896501</v>
+        <v>124894199</v>
       </c>
       <c r="B5" t="n">
         <v>79891</v>
@@ -1074,10 +1074,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>477773</v>
+        <v>477872</v>
       </c>
       <c r="R5" t="n">
-        <v>6600569</v>
+        <v>6600787</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1109,7 +1109,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>14:42</t>
+          <t>13:27</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1119,12 +1119,12 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>14:42</t>
+          <t>13:27</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>På lönnlåga.</t>
+          <t>På senvuxen asp.</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1151,10 +1151,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>124894766</v>
+        <v>124896501</v>
       </c>
       <c r="B6" t="n">
-        <v>79920</v>
+        <v>79891</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1163,25 +1163,25 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6462</v>
+        <v>6458</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1191,10 +1191,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>477763</v>
+        <v>477773</v>
       </c>
       <c r="R6" t="n">
-        <v>6600615</v>
+        <v>6600569</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1226,7 +1226,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>13:47</t>
+          <t>14:42</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1236,12 +1236,12 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>13:47</t>
+          <t>14:42</t>
         </is>
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>På senvuxen skogslönn.</t>
+          <t>På lönnlåga.</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1268,10 +1268,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>124894199</v>
+        <v>124894766</v>
       </c>
       <c r="B7" t="n">
-        <v>79891</v>
+        <v>79920</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1280,25 +1280,25 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6458</v>
+        <v>6462</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1308,10 +1308,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>477872</v>
+        <v>477763</v>
       </c>
       <c r="R7" t="n">
-        <v>6600787</v>
+        <v>6600615</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1343,7 +1343,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>13:27</t>
+          <t>13:47</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1353,12 +1353,12 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>13:27</t>
+          <t>13:47</t>
         </is>
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>På senvuxen asp.</t>
+          <t>På senvuxen skogslönn.</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1385,7 +1385,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>124895691</v>
+        <v>124894896</v>
       </c>
       <c r="B8" t="n">
         <v>79920</v>
@@ -1425,10 +1425,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>477824</v>
+        <v>477763</v>
       </c>
       <c r="R8" t="n">
-        <v>6600570</v>
+        <v>6600590</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1460,7 +1460,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>14:14</t>
+          <t>13:51</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1470,12 +1470,12 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>14:14</t>
+          <t>13:51</t>
         </is>
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>På senvuxen rönn.</t>
+          <t>På gammal rönn.</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1628,14 +1628,14 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>124891456</v>
+        <v>124891544</v>
       </c>
       <c r="B10" t="n">
         <v>56722</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Godkänd baserat på observatörens uppgifter</t>
+          <t>Behöver inte valideras</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1678,7 +1678,7 @@
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>färsk spillning</t>
+          <t>äldre spillning</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
@@ -1687,10 +1687,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>477820</v>
+        <v>477831</v>
       </c>
       <c r="R10" t="n">
-        <v>6600930</v>
+        <v>6600928</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1722,7 +1722,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>11:51</t>
+          <t>11:53</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1732,7 +1732,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>11:51</t>
+          <t>11:53</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1759,7 +1759,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>124891544</v>
+        <v>124891426</v>
       </c>
       <c r="B11" t="n">
         <v>56722</v>
@@ -1818,10 +1818,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>477831</v>
+        <v>477819</v>
       </c>
       <c r="R11" t="n">
-        <v>6600928</v>
+        <v>6600933</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1853,7 +1853,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>11:53</t>
+          <t>11:51</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1863,7 +1863,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>11:53</t>
+          <t>11:51</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1890,14 +1890,14 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>124891426</v>
+        <v>124891456</v>
       </c>
       <c r="B12" t="n">
         <v>56722</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Behöver inte valideras</t>
+          <t>Godkänd baserat på observatörens uppgifter</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1940,7 +1940,7 @@
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>äldre spillning</t>
+          <t>färsk spillning</t>
         </is>
       </c>
       <c r="P12" t="inlineStr">
@@ -1949,10 +1949,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>477819</v>
+        <v>477820</v>
       </c>
       <c r="R12" t="n">
-        <v>6600933</v>
+        <v>6600930</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -2021,10 +2021,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>125221043</v>
+        <v>125221042</v>
       </c>
       <c r="B13" t="n">
-        <v>95345</v>
+        <v>79891</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -2033,30 +2033,30 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>2810</v>
+        <v>6458</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Västlig hakmossa</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Rhytidiadelphus loreus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Hedw.) Warnst.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>5</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
@@ -2065,10 +2065,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>477772</v>
+        <v>477797</v>
       </c>
       <c r="R13" t="n">
-        <v>6600570</v>
+        <v>6600851</v>
       </c>
       <c r="S13" t="n">
         <v>5</v>
@@ -2127,7 +2127,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>125221042</v>
+        <v>125221044</v>
       </c>
       <c r="B14" t="n">
         <v>79891</v>
@@ -2171,10 +2171,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>477797</v>
+        <v>477770</v>
       </c>
       <c r="R14" t="n">
-        <v>6600851</v>
+        <v>6600573</v>
       </c>
       <c r="S14" t="n">
         <v>5</v>
@@ -2233,10 +2233,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>125221044</v>
+        <v>125221043</v>
       </c>
       <c r="B15" t="n">
-        <v>79891</v>
+        <v>95345</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2245,30 +2245,30 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6458</v>
+        <v>2810</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Västlig hakmossa</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Rhytidiadelphus loreus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Hedw.) Warnst.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>1</t>
         </is>
       </c>
       <c r="P15" t="inlineStr">
@@ -2277,10 +2277,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>477770</v>
+        <v>477772</v>
       </c>
       <c r="R15" t="n">
-        <v>6600573</v>
+        <v>6600570</v>
       </c>
       <c r="S15" t="n">
         <v>5</v>

--- a/artfynd/A 22053-2021 artfynd.xlsx
+++ b/artfynd/A 22053-2021 artfynd.xlsx
@@ -792,10 +792,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>124895183</v>
+        <v>124894199</v>
       </c>
       <c r="B3" t="n">
-        <v>79851</v>
+        <v>79891</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -804,41 +804,38 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>229497</v>
+        <v>6458</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="J3" t="inlineStr"/>
-      <c r="K3" t="inlineStr"/>
-      <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Krontorp, Vstm</t>
+          <t>Krontorp, Krontorp, Vstm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>477758</v>
+        <v>477872</v>
       </c>
       <c r="R3" t="n">
-        <v>6600583</v>
+        <v>6600787</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -870,7 +867,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>13:27</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -880,12 +877,12 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>13:27</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>På senvuxen skogslönn.</t>
+          <t>På senvuxen asp.</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -894,7 +891,6 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
-      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
@@ -913,7 +909,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>124895297</v>
+        <v>124896501</v>
       </c>
       <c r="B4" t="n">
         <v>79891</v>
@@ -947,19 +943,16 @@
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="J4" t="inlineStr"/>
-      <c r="K4" t="inlineStr"/>
-      <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
           <t>Krontorp, Krontorp, Vstm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>477767</v>
+        <v>477773</v>
       </c>
       <c r="R4" t="n">
-        <v>6600581</v>
+        <v>6600569</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -991,7 +984,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>14:02</t>
+          <t>14:42</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1001,7 +994,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>14:02</t>
+          <t>14:42</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">
@@ -1015,7 +1008,6 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
-      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
@@ -1034,10 +1026,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>124894199</v>
+        <v>124894766</v>
       </c>
       <c r="B5" t="n">
-        <v>79891</v>
+        <v>79920</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1046,25 +1038,25 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6458</v>
+        <v>6462</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1074,10 +1066,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>477872</v>
+        <v>477763</v>
       </c>
       <c r="R5" t="n">
-        <v>6600787</v>
+        <v>6600615</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1109,7 +1101,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>13:27</t>
+          <t>13:47</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1119,12 +1111,12 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>13:27</t>
+          <t>13:47</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>På senvuxen asp.</t>
+          <t>På senvuxen skogslönn.</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1151,7 +1143,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>124896501</v>
+        <v>124895297</v>
       </c>
       <c r="B6" t="n">
         <v>79891</v>
@@ -1185,16 +1177,19 @@
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr"/>
+      <c r="K6" t="inlineStr"/>
+      <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
           <t>Krontorp, Krontorp, Vstm</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>477773</v>
+        <v>477767</v>
       </c>
       <c r="R6" t="n">
-        <v>6600569</v>
+        <v>6600581</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1226,7 +1221,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>14:42</t>
+          <t>14:02</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1236,7 +1231,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>14:42</t>
+          <t>14:02</t>
         </is>
       </c>
       <c r="AC6" t="inlineStr">
@@ -1250,6 +1245,7 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
+      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
@@ -1268,7 +1264,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>124894766</v>
+        <v>124894896</v>
       </c>
       <c r="B7" t="n">
         <v>79920</v>
@@ -1311,7 +1307,7 @@
         <v>477763</v>
       </c>
       <c r="R7" t="n">
-        <v>6600615</v>
+        <v>6600590</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1343,7 +1339,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>13:47</t>
+          <t>13:51</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1353,12 +1349,12 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>13:47</t>
+          <t>13:51</t>
         </is>
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>På senvuxen skogslönn.</t>
+          <t>På gammal rönn.</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1385,10 +1381,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>124894896</v>
+        <v>124895183</v>
       </c>
       <c r="B8" t="n">
-        <v>79920</v>
+        <v>79851</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1401,34 +1397,37 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6462</v>
+        <v>229497</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
+      <c r="J8" t="inlineStr"/>
+      <c r="K8" t="inlineStr"/>
+      <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Krontorp, Krontorp, Vstm</t>
+          <t>Krontorp, Vstm</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>477763</v>
+        <v>477758</v>
       </c>
       <c r="R8" t="n">
-        <v>6600590</v>
+        <v>6600583</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1460,7 +1459,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>13:51</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1470,12 +1469,12 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>13:51</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>På gammal rönn.</t>
+          <t>På senvuxen skogslönn.</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1484,6 +1483,7 @@
       <c r="AE8" t="b">
         <v>0</v>
       </c>
+      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>
@@ -2021,10 +2021,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>125221042</v>
+        <v>125221041</v>
       </c>
       <c r="B13" t="n">
-        <v>79891</v>
+        <v>79892</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -2037,26 +2037,26 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6458</v>
+        <v>2081</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>1</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
@@ -2065,10 +2065,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>477797</v>
+        <v>477795</v>
       </c>
       <c r="R13" t="n">
-        <v>6600851</v>
+        <v>6600854</v>
       </c>
       <c r="S13" t="n">
         <v>5</v>
@@ -2127,10 +2127,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>125221044</v>
+        <v>125221043</v>
       </c>
       <c r="B14" t="n">
-        <v>79891</v>
+        <v>95345</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2139,30 +2139,30 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6458</v>
+        <v>2810</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Västlig hakmossa</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Rhytidiadelphus loreus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Hedw.) Warnst.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>1</t>
         </is>
       </c>
       <c r="P14" t="inlineStr">
@@ -2171,10 +2171,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>477770</v>
+        <v>477772</v>
       </c>
       <c r="R14" t="n">
-        <v>6600573</v>
+        <v>6600570</v>
       </c>
       <c r="S14" t="n">
         <v>5</v>
@@ -2233,10 +2233,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>125221043</v>
+        <v>125221044</v>
       </c>
       <c r="B15" t="n">
-        <v>95345</v>
+        <v>79891</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2245,30 +2245,30 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>2810</v>
+        <v>6458</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Västlig hakmossa</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Rhytidiadelphus loreus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Hedw.) Warnst.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>5</t>
         </is>
       </c>
       <c r="P15" t="inlineStr">
@@ -2277,10 +2277,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>477772</v>
+        <v>477770</v>
       </c>
       <c r="R15" t="n">
-        <v>6600570</v>
+        <v>6600573</v>
       </c>
       <c r="S15" t="n">
         <v>5</v>
@@ -2339,10 +2339,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>125221041</v>
+        <v>125221042</v>
       </c>
       <c r="B16" t="n">
-        <v>79892</v>
+        <v>79891</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2355,26 +2355,26 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>2081</v>
+        <v>6458</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>5</t>
         </is>
       </c>
       <c r="P16" t="inlineStr">
@@ -2383,10 +2383,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>477795</v>
+        <v>477797</v>
       </c>
       <c r="R16" t="n">
-        <v>6600854</v>
+        <v>6600851</v>
       </c>
       <c r="S16" t="n">
         <v>5</v>

--- a/artfynd/A 22053-2021 artfynd.xlsx
+++ b/artfynd/A 22053-2021 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>124895691</v>
+        <v>124894199</v>
       </c>
       <c r="B2" t="n">
-        <v>79920</v>
+        <v>79891</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,25 +687,25 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6462</v>
+        <v>6458</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>477824</v>
+        <v>477872</v>
       </c>
       <c r="R2" t="n">
-        <v>6600570</v>
+        <v>6600787</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -750,7 +750,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>14:14</t>
+          <t>13:27</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -760,12 +760,12 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>14:14</t>
+          <t>13:27</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>På senvuxen rönn.</t>
+          <t>På senvuxen asp.</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -792,7 +792,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>124894199</v>
+        <v>124895297</v>
       </c>
       <c r="B3" t="n">
         <v>79891</v>
@@ -826,16 +826,19 @@
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr"/>
+      <c r="K3" t="inlineStr"/>
+      <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
           <t>Krontorp, Krontorp, Vstm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>477872</v>
+        <v>477767</v>
       </c>
       <c r="R3" t="n">
-        <v>6600787</v>
+        <v>6600581</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -867,7 +870,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>13:27</t>
+          <t>14:02</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -877,12 +880,12 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>13:27</t>
+          <t>14:02</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>På senvuxen asp.</t>
+          <t>På lönnlåga.</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -891,6 +894,7 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
+      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
@@ -909,10 +913,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>124896501</v>
+        <v>124895183</v>
       </c>
       <c r="B4" t="n">
-        <v>79891</v>
+        <v>79851</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -921,38 +925,41 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6458</v>
+        <v>229497</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr"/>
+      <c r="K4" t="inlineStr"/>
+      <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Krontorp, Krontorp, Vstm</t>
+          <t>Krontorp, Vstm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>477773</v>
+        <v>477758</v>
       </c>
       <c r="R4" t="n">
-        <v>6600569</v>
+        <v>6600583</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -984,7 +991,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>14:42</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -994,12 +1001,12 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>14:42</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>På lönnlåga.</t>
+          <t>På senvuxen skogslönn.</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1008,6 +1015,7 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
+      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
@@ -1026,7 +1034,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>124894766</v>
+        <v>124895691</v>
       </c>
       <c r="B5" t="n">
         <v>79920</v>
@@ -1066,10 +1074,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>477763</v>
+        <v>477824</v>
       </c>
       <c r="R5" t="n">
-        <v>6600615</v>
+        <v>6600570</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1101,7 +1109,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>13:47</t>
+          <t>14:14</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1111,12 +1119,12 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>13:47</t>
+          <t>14:14</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>På senvuxen skogslönn.</t>
+          <t>På senvuxen rönn.</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1143,10 +1151,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>124895297</v>
+        <v>124894896</v>
       </c>
       <c r="B6" t="n">
-        <v>79891</v>
+        <v>79920</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1155,41 +1163,38 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6458</v>
+        <v>6462</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
-      <c r="J6" t="inlineStr"/>
-      <c r="K6" t="inlineStr"/>
-      <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
           <t>Krontorp, Krontorp, Vstm</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>477767</v>
+        <v>477763</v>
       </c>
       <c r="R6" t="n">
-        <v>6600581</v>
+        <v>6600590</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1221,7 +1226,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>14:02</t>
+          <t>13:51</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1231,12 +1236,12 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>14:02</t>
+          <t>13:51</t>
         </is>
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>På lönnlåga.</t>
+          <t>På gammal rönn.</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1245,7 +1250,6 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
-      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
@@ -1264,7 +1268,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>124894896</v>
+        <v>124894766</v>
       </c>
       <c r="B7" t="n">
         <v>79920</v>
@@ -1307,7 +1311,7 @@
         <v>477763</v>
       </c>
       <c r="R7" t="n">
-        <v>6600590</v>
+        <v>6600615</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1339,7 +1343,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>13:51</t>
+          <t>13:47</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1349,12 +1353,12 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>13:51</t>
+          <t>13:47</t>
         </is>
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>På gammal rönn.</t>
+          <t>På senvuxen skogslönn.</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1381,10 +1385,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>124895183</v>
+        <v>124896501</v>
       </c>
       <c r="B8" t="n">
-        <v>79851</v>
+        <v>79891</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1393,41 +1397,38 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>229497</v>
+        <v>6458</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
-      <c r="J8" t="inlineStr"/>
-      <c r="K8" t="inlineStr"/>
-      <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Krontorp, Vstm</t>
+          <t>Krontorp, Krontorp, Vstm</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>477758</v>
+        <v>477773</v>
       </c>
       <c r="R8" t="n">
-        <v>6600583</v>
+        <v>6600569</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1459,7 +1460,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>14:42</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1469,12 +1470,12 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>14:42</t>
         </is>
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>På senvuxen skogslönn.</t>
+          <t>På lönnlåga.</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1483,7 +1484,6 @@
       <c r="AE8" t="b">
         <v>0</v>
       </c>
-      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>
@@ -1628,14 +1628,14 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>124891544</v>
+        <v>124891456</v>
       </c>
       <c r="B10" t="n">
         <v>56722</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Behöver inte valideras</t>
+          <t>Godkänd baserat på observatörens uppgifter</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1678,7 +1678,7 @@
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>äldre spillning</t>
+          <t>färsk spillning</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
@@ -1687,10 +1687,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>477831</v>
+        <v>477820</v>
       </c>
       <c r="R10" t="n">
-        <v>6600928</v>
+        <v>6600930</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1722,7 +1722,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>11:53</t>
+          <t>11:51</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1732,7 +1732,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>11:53</t>
+          <t>11:51</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1890,14 +1890,14 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>124891456</v>
+        <v>124891544</v>
       </c>
       <c r="B12" t="n">
         <v>56722</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Godkänd baserat på observatörens uppgifter</t>
+          <t>Behöver inte valideras</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1940,7 +1940,7 @@
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>färsk spillning</t>
+          <t>äldre spillning</t>
         </is>
       </c>
       <c r="P12" t="inlineStr">
@@ -1949,10 +1949,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>477820</v>
+        <v>477831</v>
       </c>
       <c r="R12" t="n">
-        <v>6600930</v>
+        <v>6600928</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1984,7 +1984,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>11:51</t>
+          <t>11:53</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1994,7 +1994,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>11:51</t>
+          <t>11:53</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -2021,10 +2021,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>125221041</v>
+        <v>125221042</v>
       </c>
       <c r="B13" t="n">
-        <v>79892</v>
+        <v>79891</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -2037,26 +2037,26 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>2081</v>
+        <v>6458</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>5</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
@@ -2065,10 +2065,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>477795</v>
+        <v>477797</v>
       </c>
       <c r="R13" t="n">
-        <v>6600854</v>
+        <v>6600851</v>
       </c>
       <c r="S13" t="n">
         <v>5</v>
@@ -2127,10 +2127,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>125221043</v>
+        <v>125221044</v>
       </c>
       <c r="B14" t="n">
-        <v>95345</v>
+        <v>79891</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2139,30 +2139,30 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>2810</v>
+        <v>6458</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Västlig hakmossa</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Rhytidiadelphus loreus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Hedw.) Warnst.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>5</t>
         </is>
       </c>
       <c r="P14" t="inlineStr">
@@ -2171,10 +2171,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>477772</v>
+        <v>477770</v>
       </c>
       <c r="R14" t="n">
-        <v>6600570</v>
+        <v>6600573</v>
       </c>
       <c r="S14" t="n">
         <v>5</v>
@@ -2233,10 +2233,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>125221044</v>
+        <v>125221041</v>
       </c>
       <c r="B15" t="n">
-        <v>79891</v>
+        <v>79892</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2249,26 +2249,26 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6458</v>
+        <v>2081</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>1</t>
         </is>
       </c>
       <c r="P15" t="inlineStr">
@@ -2277,10 +2277,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>477770</v>
+        <v>477795</v>
       </c>
       <c r="R15" t="n">
-        <v>6600573</v>
+        <v>6600854</v>
       </c>
       <c r="S15" t="n">
         <v>5</v>
@@ -2339,10 +2339,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>125221042</v>
+        <v>125221043</v>
       </c>
       <c r="B16" t="n">
-        <v>79891</v>
+        <v>95345</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2351,30 +2351,30 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6458</v>
+        <v>2810</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Västlig hakmossa</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Rhytidiadelphus loreus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Hedw.) Warnst.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>1</t>
         </is>
       </c>
       <c r="P16" t="inlineStr">
@@ -2383,10 +2383,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>477797</v>
+        <v>477772</v>
       </c>
       <c r="R16" t="n">
-        <v>6600851</v>
+        <v>6600570</v>
       </c>
       <c r="S16" t="n">
         <v>5</v>

--- a/artfynd/A 22053-2021 artfynd.xlsx
+++ b/artfynd/A 22053-2021 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>124894199</v>
+        <v>124895297</v>
       </c>
       <c r="B2" t="n">
         <v>79891</v>
@@ -709,16 +709,19 @@
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr"/>
+      <c r="K2" t="inlineStr"/>
+      <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
           <t>Krontorp, Krontorp, Vstm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>477872</v>
+        <v>477767</v>
       </c>
       <c r="R2" t="n">
-        <v>6600787</v>
+        <v>6600581</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -750,7 +753,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>13:27</t>
+          <t>14:02</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -760,12 +763,12 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>13:27</t>
+          <t>14:02</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>På senvuxen asp.</t>
+          <t>På lönnlåga.</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -774,6 +777,7 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
+      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
@@ -792,10 +796,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>124895297</v>
+        <v>124895183</v>
       </c>
       <c r="B3" t="n">
-        <v>79891</v>
+        <v>79851</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -804,25 +808,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6458</v>
+        <v>229497</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -831,14 +835,14 @@
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Krontorp, Krontorp, Vstm</t>
+          <t>Krontorp, Vstm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>477767</v>
+        <v>477758</v>
       </c>
       <c r="R3" t="n">
-        <v>6600581</v>
+        <v>6600583</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -870,7 +874,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>14:02</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -880,12 +884,12 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>14:02</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>På lönnlåga.</t>
+          <t>På senvuxen skogslönn.</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -913,10 +917,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>124895183</v>
+        <v>124896501</v>
       </c>
       <c r="B4" t="n">
-        <v>79851</v>
+        <v>79891</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -925,41 +929,38 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>229497</v>
+        <v>6458</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="J4" t="inlineStr"/>
-      <c r="K4" t="inlineStr"/>
-      <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Krontorp, Vstm</t>
+          <t>Krontorp, Krontorp, Vstm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>477758</v>
+        <v>477773</v>
       </c>
       <c r="R4" t="n">
-        <v>6600583</v>
+        <v>6600569</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -991,7 +992,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>14:42</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1001,12 +1002,12 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>14:42</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>På senvuxen skogslönn.</t>
+          <t>På lönnlåga.</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1015,7 +1016,6 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
-      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
@@ -1034,7 +1034,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>124895691</v>
+        <v>124894766</v>
       </c>
       <c r="B5" t="n">
         <v>79920</v>
@@ -1074,10 +1074,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>477824</v>
+        <v>477763</v>
       </c>
       <c r="R5" t="n">
-        <v>6600570</v>
+        <v>6600615</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1109,7 +1109,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>14:14</t>
+          <t>13:47</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1119,12 +1119,12 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>14:14</t>
+          <t>13:47</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>På senvuxen rönn.</t>
+          <t>På senvuxen skogslönn.</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1151,10 +1151,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>124894896</v>
+        <v>124894199</v>
       </c>
       <c r="B6" t="n">
-        <v>79920</v>
+        <v>79891</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1163,25 +1163,25 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6462</v>
+        <v>6458</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1191,10 +1191,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>477763</v>
+        <v>477872</v>
       </c>
       <c r="R6" t="n">
-        <v>6600590</v>
+        <v>6600787</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1226,7 +1226,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>13:51</t>
+          <t>13:27</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1236,12 +1236,12 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>13:51</t>
+          <t>13:27</t>
         </is>
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>På gammal rönn.</t>
+          <t>På senvuxen asp.</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1268,7 +1268,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>124894766</v>
+        <v>124895691</v>
       </c>
       <c r="B7" t="n">
         <v>79920</v>
@@ -1308,10 +1308,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>477763</v>
+        <v>477824</v>
       </c>
       <c r="R7" t="n">
-        <v>6600615</v>
+        <v>6600570</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1343,7 +1343,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>13:47</t>
+          <t>14:14</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1353,12 +1353,12 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>13:47</t>
+          <t>14:14</t>
         </is>
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>På senvuxen skogslönn.</t>
+          <t>På senvuxen rönn.</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1385,10 +1385,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>124896501</v>
+        <v>124894896</v>
       </c>
       <c r="B8" t="n">
-        <v>79891</v>
+        <v>79920</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1397,25 +1397,25 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6458</v>
+        <v>6462</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1425,10 +1425,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>477773</v>
+        <v>477763</v>
       </c>
       <c r="R8" t="n">
-        <v>6600569</v>
+        <v>6600590</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1460,7 +1460,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>14:42</t>
+          <t>13:51</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1470,12 +1470,12 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>14:42</t>
+          <t>13:51</t>
         </is>
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>På lönnlåga.</t>
+          <t>På gammal rönn.</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1628,14 +1628,14 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>124891456</v>
+        <v>124891426</v>
       </c>
       <c r="B10" t="n">
         <v>56722</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Godkänd baserat på observatörens uppgifter</t>
+          <t>Behöver inte valideras</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1678,7 +1678,7 @@
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>färsk spillning</t>
+          <t>äldre spillning</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
@@ -1687,10 +1687,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>477820</v>
+        <v>477819</v>
       </c>
       <c r="R10" t="n">
-        <v>6600930</v>
+        <v>6600933</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1759,14 +1759,14 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>124891426</v>
+        <v>124891456</v>
       </c>
       <c r="B11" t="n">
         <v>56722</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Behöver inte valideras</t>
+          <t>Godkänd baserat på observatörens uppgifter</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1809,7 +1809,7 @@
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>äldre spillning</t>
+          <t>färsk spillning</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
@@ -1818,10 +1818,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>477819</v>
+        <v>477820</v>
       </c>
       <c r="R11" t="n">
-        <v>6600933</v>
+        <v>6600930</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>

--- a/artfynd/A 22053-2021 artfynd.xlsx
+++ b/artfynd/A 22053-2021 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>124895297</v>
+        <v>124896501</v>
       </c>
       <c r="B2" t="n">
-        <v>79891</v>
+        <v>80028</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -709,19 +709,16 @@
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
-      <c r="J2" t="inlineStr"/>
-      <c r="K2" t="inlineStr"/>
-      <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
           <t>Krontorp, Krontorp, Vstm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>477767</v>
+        <v>477773</v>
       </c>
       <c r="R2" t="n">
-        <v>6600581</v>
+        <v>6600569</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -753,7 +750,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>14:02</t>
+          <t>14:42</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -763,7 +760,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>14:02</t>
+          <t>14:42</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
@@ -777,7 +774,6 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
-      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
@@ -796,10 +792,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>124895183</v>
+        <v>124894896</v>
       </c>
       <c r="B3" t="n">
-        <v>79851</v>
+        <v>80057</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -812,37 +808,34 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>229497</v>
+        <v>6462</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="J3" t="inlineStr"/>
-      <c r="K3" t="inlineStr"/>
-      <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Krontorp, Vstm</t>
+          <t>Krontorp, Krontorp, Vstm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>477758</v>
+        <v>477763</v>
       </c>
       <c r="R3" t="n">
-        <v>6600583</v>
+        <v>6600590</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -874,7 +867,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>13:51</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -884,12 +877,12 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>13:51</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>På senvuxen skogslönn.</t>
+          <t>På gammal rönn.</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -898,7 +891,6 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
-      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
@@ -917,10 +909,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>124896501</v>
+        <v>124894199</v>
       </c>
       <c r="B4" t="n">
-        <v>79891</v>
+        <v>80028</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -957,10 +949,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>477773</v>
+        <v>477872</v>
       </c>
       <c r="R4" t="n">
-        <v>6600569</v>
+        <v>6600787</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -992,7 +984,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>14:42</t>
+          <t>13:27</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1002,12 +994,12 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>14:42</t>
+          <t>13:27</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>På lönnlåga.</t>
+          <t>På senvuxen asp.</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1034,10 +1026,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>124894766</v>
+        <v>124895150</v>
       </c>
       <c r="B5" t="n">
-        <v>79920</v>
+        <v>80028</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1046,25 +1038,25 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6462</v>
+        <v>6458</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1074,10 +1066,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>477763</v>
+        <v>477767</v>
       </c>
       <c r="R5" t="n">
-        <v>6600615</v>
+        <v>6600581</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1109,7 +1101,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>13:47</t>
+          <t>13:59</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1119,7 +1111,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>13:47</t>
+          <t>13:59</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr">
@@ -1151,10 +1143,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>124894199</v>
+        <v>124895183</v>
       </c>
       <c r="B6" t="n">
-        <v>79891</v>
+        <v>79988</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1163,38 +1155,41 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6458</v>
+        <v>229497</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr"/>
+      <c r="K6" t="inlineStr"/>
+      <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Krontorp, Krontorp, Vstm</t>
+          <t>Krontorp, Vstm</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>477872</v>
+        <v>477758</v>
       </c>
       <c r="R6" t="n">
-        <v>6600787</v>
+        <v>6600583</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1226,7 +1221,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>13:27</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1236,12 +1231,12 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>13:27</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>På senvuxen asp.</t>
+          <t>På senvuxen skogslönn.</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1250,6 +1245,7 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
+      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
@@ -1271,7 +1267,7 @@
         <v>124895691</v>
       </c>
       <c r="B7" t="n">
-        <v>79920</v>
+        <v>80057</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1385,10 +1381,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>124894896</v>
+        <v>124894766</v>
       </c>
       <c r="B8" t="n">
-        <v>79920</v>
+        <v>80057</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1428,7 +1424,7 @@
         <v>477763</v>
       </c>
       <c r="R8" t="n">
-        <v>6600590</v>
+        <v>6600615</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1460,7 +1456,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>13:51</t>
+          <t>13:47</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1470,12 +1466,12 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>13:51</t>
+          <t>13:47</t>
         </is>
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>På gammal rönn.</t>
+          <t>På senvuxen skogslönn.</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1502,37 +1498,37 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>124895742</v>
+        <v>124891544</v>
       </c>
       <c r="B9" t="n">
-        <v>57529</v>
+        <v>56836</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Godkänd baserat på observatörens uppgifter</t>
+          <t>Behöver inte valideras</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100049</v>
+        <v>100138</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -1545,9 +1541,14 @@
           <t>adult</t>
         </is>
       </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>äldre spillning</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
@@ -1556,10 +1557,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>477824</v>
+        <v>477831</v>
       </c>
       <c r="R9" t="n">
-        <v>6600570</v>
+        <v>6600928</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1591,7 +1592,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>14:17</t>
+          <t>11:53</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1601,7 +1602,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>14:17</t>
+          <t>11:53</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1631,7 +1632,7 @@
         <v>124891426</v>
       </c>
       <c r="B10" t="n">
-        <v>56722</v>
+        <v>56836</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1759,10 +1760,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>124891456</v>
+        <v>124895742</v>
       </c>
       <c r="B11" t="n">
-        <v>56722</v>
+        <v>57632</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1771,25 +1772,25 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100138</v>
+        <v>100049</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -1802,14 +1803,9 @@
           <t>adult</t>
         </is>
       </c>
-      <c r="L11" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>färsk spillning</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
@@ -1818,10 +1814,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>477820</v>
+        <v>477824</v>
       </c>
       <c r="R11" t="n">
-        <v>6600930</v>
+        <v>6600570</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1853,7 +1849,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>11:51</t>
+          <t>14:17</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1863,7 +1859,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>11:51</t>
+          <t>14:17</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1890,14 +1886,14 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>124891544</v>
+        <v>124891456</v>
       </c>
       <c r="B12" t="n">
-        <v>56722</v>
+        <v>56836</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Behöver inte valideras</t>
+          <t>Godkänd baserat på observatörens uppgifter</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1940,7 +1936,7 @@
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>äldre spillning</t>
+          <t>färsk spillning</t>
         </is>
       </c>
       <c r="P12" t="inlineStr">
@@ -1949,10 +1945,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>477831</v>
+        <v>477820</v>
       </c>
       <c r="R12" t="n">
-        <v>6600928</v>
+        <v>6600930</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1984,7 +1980,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>11:53</t>
+          <t>11:51</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1994,7 +1990,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>11:53</t>
+          <t>11:51</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -2021,10 +2017,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>125221042</v>
+        <v>125221044</v>
       </c>
       <c r="B13" t="n">
-        <v>79891</v>
+        <v>80028</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -2065,10 +2061,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>477797</v>
+        <v>477770</v>
       </c>
       <c r="R13" t="n">
-        <v>6600851</v>
+        <v>6600573</v>
       </c>
       <c r="S13" t="n">
         <v>5</v>
@@ -2127,10 +2123,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>125221044</v>
+        <v>125221041</v>
       </c>
       <c r="B14" t="n">
-        <v>79891</v>
+        <v>80029</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2143,26 +2139,26 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6458</v>
+        <v>2081</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>1</t>
         </is>
       </c>
       <c r="P14" t="inlineStr">
@@ -2171,10 +2167,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>477770</v>
+        <v>477795</v>
       </c>
       <c r="R14" t="n">
-        <v>6600573</v>
+        <v>6600854</v>
       </c>
       <c r="S14" t="n">
         <v>5</v>
@@ -2233,10 +2229,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>125221041</v>
+        <v>125221042</v>
       </c>
       <c r="B15" t="n">
-        <v>79892</v>
+        <v>80028</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2249,26 +2245,26 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>2081</v>
+        <v>6458</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>5</t>
         </is>
       </c>
       <c r="P15" t="inlineStr">
@@ -2277,10 +2273,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>477795</v>
+        <v>477797</v>
       </c>
       <c r="R15" t="n">
-        <v>6600854</v>
+        <v>6600851</v>
       </c>
       <c r="S15" t="n">
         <v>5</v>
@@ -2342,7 +2338,7 @@
         <v>125221043</v>
       </c>
       <c r="B16" t="n">
-        <v>95345</v>
+        <v>95513</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>

--- a/artfynd/A 22053-2021 artfynd.xlsx
+++ b/artfynd/A 22053-2021 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>124896501</v>
+        <v>124895183</v>
       </c>
       <c r="B2" t="n">
-        <v>80028</v>
+        <v>79988</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,38 +687,41 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6458</v>
+        <v>229497</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr"/>
+      <c r="K2" t="inlineStr"/>
+      <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Krontorp, Krontorp, Vstm</t>
+          <t>Krontorp, Vstm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>477773</v>
+        <v>477758</v>
       </c>
       <c r="R2" t="n">
-        <v>6600569</v>
+        <v>6600583</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -750,7 +753,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>14:42</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -760,12 +763,12 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>14:42</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>På lönnlåga.</t>
+          <t>På senvuxen skogslönn.</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -774,6 +777,7 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
+      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
@@ -792,10 +796,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>124894896</v>
+        <v>124894199</v>
       </c>
       <c r="B3" t="n">
-        <v>80057</v>
+        <v>80028</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -804,25 +808,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6462</v>
+        <v>6458</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -832,10 +836,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>477763</v>
+        <v>477872</v>
       </c>
       <c r="R3" t="n">
-        <v>6600590</v>
+        <v>6600787</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -867,7 +871,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>13:51</t>
+          <t>13:27</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -877,12 +881,12 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>13:51</t>
+          <t>13:27</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>På gammal rönn.</t>
+          <t>På senvuxen asp.</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -909,7 +913,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>124894199</v>
+        <v>124896501</v>
       </c>
       <c r="B4" t="n">
         <v>80028</v>
@@ -949,10 +953,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>477872</v>
+        <v>477773</v>
       </c>
       <c r="R4" t="n">
-        <v>6600787</v>
+        <v>6600569</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -984,7 +988,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>13:27</t>
+          <t>14:42</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -994,12 +998,12 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>13:27</t>
+          <t>14:42</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>På senvuxen asp.</t>
+          <t>På lönnlåga.</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1026,10 +1030,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>124895150</v>
+        <v>124894896</v>
       </c>
       <c r="B5" t="n">
-        <v>80028</v>
+        <v>80057</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1038,25 +1042,25 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6458</v>
+        <v>6462</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1066,10 +1070,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>477767</v>
+        <v>477763</v>
       </c>
       <c r="R5" t="n">
-        <v>6600581</v>
+        <v>6600590</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1101,7 +1105,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>13:59</t>
+          <t>13:51</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1111,12 +1115,12 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>13:59</t>
+          <t>13:51</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>På senvuxen skogslönn.</t>
+          <t>På gammal rönn.</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1143,10 +1147,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>124895183</v>
+        <v>124895150</v>
       </c>
       <c r="B6" t="n">
-        <v>79988</v>
+        <v>80028</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1155,41 +1159,38 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>229497</v>
+        <v>6458</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
-      <c r="J6" t="inlineStr"/>
-      <c r="K6" t="inlineStr"/>
-      <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Krontorp, Vstm</t>
+          <t>Krontorp, Krontorp, Vstm</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>477758</v>
+        <v>477767</v>
       </c>
       <c r="R6" t="n">
-        <v>6600583</v>
+        <v>6600581</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1221,7 +1222,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>13:59</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1231,7 +1232,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>13:59</t>
         </is>
       </c>
       <c r="AC6" t="inlineStr">
@@ -1245,7 +1246,6 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
-      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
@@ -1498,7 +1498,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>124891544</v>
+        <v>124891426</v>
       </c>
       <c r="B9" t="n">
         <v>56836</v>
@@ -1557,10 +1557,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>477831</v>
+        <v>477819</v>
       </c>
       <c r="R9" t="n">
-        <v>6600928</v>
+        <v>6600933</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1592,7 +1592,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>11:53</t>
+          <t>11:51</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1602,7 +1602,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>11:53</t>
+          <t>11:51</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1629,37 +1629,37 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>124891426</v>
+        <v>124895742</v>
       </c>
       <c r="B10" t="n">
-        <v>56836</v>
+        <v>57632</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Behöver inte valideras</t>
+          <t>Godkänd baserat på observatörens uppgifter</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100138</v>
+        <v>100049</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -1672,14 +1672,9 @@
           <t>adult</t>
         </is>
       </c>
-      <c r="L10" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>äldre spillning</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
@@ -1688,10 +1683,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>477819</v>
+        <v>477824</v>
       </c>
       <c r="R10" t="n">
-        <v>6600933</v>
+        <v>6600570</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1723,7 +1718,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>11:51</t>
+          <t>14:17</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1733,7 +1728,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>11:51</t>
+          <t>14:17</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1760,37 +1755,37 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>124895742</v>
+        <v>124891544</v>
       </c>
       <c r="B11" t="n">
-        <v>57632</v>
+        <v>56836</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Godkänd baserat på observatörens uppgifter</t>
+          <t>Behöver inte valideras</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100049</v>
+        <v>100138</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -1803,9 +1798,14 @@
           <t>adult</t>
         </is>
       </c>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>äldre spillning</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
@@ -1814,10 +1814,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>477824</v>
+        <v>477831</v>
       </c>
       <c r="R11" t="n">
-        <v>6600570</v>
+        <v>6600928</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1849,7 +1849,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>14:17</t>
+          <t>11:53</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1859,7 +1859,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>14:17</t>
+          <t>11:53</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -2017,10 +2017,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>125221044</v>
+        <v>125221043</v>
       </c>
       <c r="B13" t="n">
-        <v>80028</v>
+        <v>95513</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -2029,30 +2029,30 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6458</v>
+        <v>2810</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Västlig hakmossa</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Rhytidiadelphus loreus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Hedw.) Warnst.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>1</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
@@ -2061,10 +2061,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>477770</v>
+        <v>477772</v>
       </c>
       <c r="R13" t="n">
-        <v>6600573</v>
+        <v>6600570</v>
       </c>
       <c r="S13" t="n">
         <v>5</v>
@@ -2229,7 +2229,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>125221042</v>
+        <v>125221044</v>
       </c>
       <c r="B15" t="n">
         <v>80028</v>
@@ -2273,10 +2273,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>477797</v>
+        <v>477770</v>
       </c>
       <c r="R15" t="n">
-        <v>6600851</v>
+        <v>6600573</v>
       </c>
       <c r="S15" t="n">
         <v>5</v>
@@ -2335,10 +2335,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>125221043</v>
+        <v>125221042</v>
       </c>
       <c r="B16" t="n">
-        <v>95513</v>
+        <v>80028</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2347,30 +2347,30 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>2810</v>
+        <v>6458</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Västlig hakmossa</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Rhytidiadelphus loreus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Hedw.) Warnst.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>5</t>
         </is>
       </c>
       <c r="P16" t="inlineStr">
@@ -2379,10 +2379,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>477772</v>
+        <v>477797</v>
       </c>
       <c r="R16" t="n">
-        <v>6600570</v>
+        <v>6600851</v>
       </c>
       <c r="S16" t="n">
         <v>5</v>

--- a/artfynd/A 22053-2021 artfynd.xlsx
+++ b/artfynd/A 22053-2021 artfynd.xlsx
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>124895183</v>
+        <v>124894896</v>
       </c>
       <c r="B2" t="n">
-        <v>79988</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80057</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,37 +686,34 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>229497</v>
+        <v>6462</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
-      <c r="J2" t="inlineStr"/>
-      <c r="K2" t="inlineStr"/>
-      <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Krontorp, Vstm</t>
+          <t>Krontorp, Krontorp, Vstm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>477758</v>
+        <v>477763</v>
       </c>
       <c r="R2" t="n">
-        <v>6600583</v>
+        <v>6600590</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -753,7 +745,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>13:51</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -763,12 +755,12 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>13:51</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>På senvuxen skogslönn.</t>
+          <t>På gammal rönn.</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -777,7 +769,6 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
-      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
@@ -801,11 +792,6 @@
       <c r="B3" t="n">
         <v>80028</v>
       </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
       <c r="D3" t="inlineStr">
         <is>
           <t>NT</t>
@@ -913,16 +899,11 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>124896501</v>
+        <v>124895150</v>
       </c>
       <c r="B4" t="n">
         <v>80028</v>
       </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
       <c r="D4" t="inlineStr">
         <is>
           <t>NT</t>
@@ -953,10 +934,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>477773</v>
+        <v>477767</v>
       </c>
       <c r="R4" t="n">
-        <v>6600569</v>
+        <v>6600581</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -988,7 +969,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>14:42</t>
+          <t>13:59</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -998,12 +979,12 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>14:42</t>
+          <t>13:59</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>På lönnlåga.</t>
+          <t>På senvuxen skogslönn.</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1030,16 +1011,11 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>124894896</v>
+        <v>124895691</v>
       </c>
       <c r="B5" t="n">
         <v>80057</v>
       </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
       <c r="D5" t="inlineStr">
         <is>
           <t>LC</t>
@@ -1070,10 +1046,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>477763</v>
+        <v>477824</v>
       </c>
       <c r="R5" t="n">
-        <v>6600590</v>
+        <v>6600570</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1105,7 +1081,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>13:51</t>
+          <t>14:14</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1115,12 +1091,12 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>13:51</t>
+          <t>14:14</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>På gammal rönn.</t>
+          <t>På senvuxen rönn.</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1147,50 +1123,48 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>124895150</v>
+        <v>124895183</v>
       </c>
       <c r="B6" t="n">
-        <v>80028</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79988</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6458</v>
+        <v>229497</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr"/>
+      <c r="K6" t="inlineStr"/>
+      <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Krontorp, Krontorp, Vstm</t>
+          <t>Krontorp, Vstm</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>477767</v>
+        <v>477758</v>
       </c>
       <c r="R6" t="n">
-        <v>6600581</v>
+        <v>6600583</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1222,7 +1196,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>13:59</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1232,7 +1206,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>13:59</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="AC6" t="inlineStr">
@@ -1246,6 +1220,7 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
+      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
@@ -1264,37 +1239,32 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>124895691</v>
+        <v>124896501</v>
       </c>
       <c r="B7" t="n">
-        <v>80057</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80028</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6462</v>
+        <v>6458</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1304,10 +1274,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>477824</v>
+        <v>477773</v>
       </c>
       <c r="R7" t="n">
-        <v>6600570</v>
+        <v>6600569</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1339,7 +1309,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>14:14</t>
+          <t>14:42</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1349,12 +1319,12 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>14:14</t>
+          <t>14:42</t>
         </is>
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>På senvuxen rönn.</t>
+          <t>På lönnlåga.</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1386,11 +1356,6 @@
       <c r="B8" t="n">
         <v>80057</v>
       </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
       <c r="D8" t="inlineStr">
         <is>
           <t>LC</t>
@@ -1498,37 +1463,32 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>124891426</v>
+        <v>124895742</v>
       </c>
       <c r="B9" t="n">
-        <v>56836</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Behöver inte valideras</t>
-        </is>
+        <v>57648</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100138</v>
+        <v>100049</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -1541,14 +1501,9 @@
           <t>adult</t>
         </is>
       </c>
-      <c r="L9" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>äldre spillning</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
@@ -1557,10 +1512,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>477819</v>
+        <v>477824</v>
       </c>
       <c r="R9" t="n">
-        <v>6600933</v>
+        <v>6600570</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1592,7 +1547,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>11:51</t>
+          <t>14:17</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1602,7 +1557,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>11:51</t>
+          <t>14:17</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1629,37 +1584,32 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>124895742</v>
+        <v>124891544</v>
       </c>
       <c r="B10" t="n">
-        <v>57632</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Godkänd baserat på observatörens uppgifter</t>
-        </is>
+        <v>56843</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100049</v>
+        <v>100138</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -1672,9 +1622,14 @@
           <t>adult</t>
         </is>
       </c>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>äldre spillning</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
@@ -1683,10 +1638,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>477824</v>
+        <v>477831</v>
       </c>
       <c r="R10" t="n">
-        <v>6600570</v>
+        <v>6600928</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1718,7 +1673,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>14:17</t>
+          <t>11:53</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1728,7 +1683,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>14:17</t>
+          <t>11:53</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1755,15 +1710,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>124891544</v>
+        <v>124891456</v>
       </c>
       <c r="B11" t="n">
-        <v>56836</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Behöver inte valideras</t>
-        </is>
+        <v>56843</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1805,7 +1755,7 @@
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>äldre spillning</t>
+          <t>färsk spillning</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
@@ -1814,10 +1764,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>477831</v>
+        <v>477820</v>
       </c>
       <c r="R11" t="n">
-        <v>6600928</v>
+        <v>6600930</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1849,7 +1799,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>11:53</t>
+          <t>11:51</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1859,7 +1809,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>11:53</t>
+          <t>11:51</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1886,15 +1836,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>124891456</v>
+        <v>124891426</v>
       </c>
       <c r="B12" t="n">
-        <v>56836</v>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Godkänd baserat på observatörens uppgifter</t>
-        </is>
+        <v>56843</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1936,7 +1881,7 @@
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>färsk spillning</t>
+          <t>äldre spillning</t>
         </is>
       </c>
       <c r="P12" t="inlineStr">
@@ -1945,10 +1890,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>477820</v>
+        <v>477819</v>
       </c>
       <c r="R12" t="n">
-        <v>6600930</v>
+        <v>6600933</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -2020,12 +1965,7 @@
         <v>125221043</v>
       </c>
       <c r="B13" t="n">
-        <v>95513</v>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>95567</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2126,12 +2066,7 @@
         <v>125221041</v>
       </c>
       <c r="B14" t="n">
-        <v>80029</v>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80071</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2229,15 +2164,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>125221044</v>
+        <v>125221042</v>
       </c>
       <c r="B15" t="n">
-        <v>80028</v>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80070</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2273,10 +2203,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>477770</v>
+        <v>477797</v>
       </c>
       <c r="R15" t="n">
-        <v>6600573</v>
+        <v>6600851</v>
       </c>
       <c r="S15" t="n">
         <v>5</v>
@@ -2335,15 +2265,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>125221042</v>
+        <v>125221044</v>
       </c>
       <c r="B16" t="n">
-        <v>80028</v>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80070</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2379,10 +2304,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>477797</v>
+        <v>477770</v>
       </c>
       <c r="R16" t="n">
-        <v>6600851</v>
+        <v>6600573</v>
       </c>
       <c r="S16" t="n">
         <v>5</v>

--- a/artfynd/A 22053-2021 artfynd.xlsx
+++ b/artfynd/A 22053-2021 artfynd.xlsx
@@ -1965,7 +1965,7 @@
         <v>125221043</v>
       </c>
       <c r="B13" t="n">
-        <v>95567</v>
+        <v>95574</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
